--- a/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104593_W15.xlsx
+++ b/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104593_W15.xlsx
@@ -565,73 +565,73 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>5.9873</v>
+        <v>5.4805</v>
       </c>
       <c r="E2" t="n">
-        <v>4.5585</v>
+        <v>4.3077</v>
       </c>
       <c r="F2" t="n">
-        <v>1.4288</v>
+        <v>1.1727</v>
       </c>
       <c r="G2" t="n">
-        <v>2.4417</v>
+        <v>2.4524</v>
       </c>
       <c r="H2" t="n">
-        <v>0.9436</v>
+        <v>0.9476</v>
       </c>
       <c r="I2" t="n">
-        <v>1.4981</v>
+        <v>1.5048</v>
       </c>
       <c r="J2" t="n">
-        <v>1.617</v>
+        <v>1.6043</v>
       </c>
       <c r="K2" t="n">
-        <v>1.7317</v>
+        <v>1.7237</v>
       </c>
       <c r="L2" t="n">
-        <v>-0.1147</v>
+        <v>-0.1194</v>
       </c>
       <c r="M2" t="n">
-        <v>0.8247</v>
+        <v>0.8481</v>
       </c>
       <c r="N2" t="n">
-        <v>-0.788</v>
+        <v>-0.7761</v>
       </c>
       <c r="O2" t="n">
-        <v>1.6127</v>
+        <v>1.6242</v>
       </c>
       <c r="P2" t="n">
-        <v>1.1342</v>
+        <v>1.1382</v>
       </c>
       <c r="Q2" t="n">
         <v>0</v>
       </c>
       <c r="R2" t="n">
-        <v>1.1342</v>
+        <v>1.1382</v>
       </c>
       <c r="S2" t="n">
-        <v>0.3868</v>
+        <v>-0.1312</v>
       </c>
       <c r="T2" t="n">
-        <v>0.7561</v>
+        <v>0.5245</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.3693</v>
+        <v>-0.6556999999999999</v>
       </c>
       <c r="V2" t="n">
-        <v>2.0246</v>
+        <v>2.0212</v>
       </c>
       <c r="W2" t="n">
-        <v>2.1853</v>
+        <v>2.1789</v>
       </c>
       <c r="X2" t="n">
-        <v>-0.1607</v>
+        <v>-0.1578</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>A. PUSTOVYI</t>
+          <t>X. CASTANEDA</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,73 +643,73 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>3.2892</v>
+        <v>3.0236</v>
       </c>
       <c r="E3" t="n">
-        <v>3.9753</v>
+        <v>3.0304</v>
       </c>
       <c r="F3" t="n">
-        <v>-0.6861</v>
+        <v>-0.0068</v>
       </c>
       <c r="G3" t="n">
-        <v>0.014</v>
+        <v>3.2386</v>
       </c>
       <c r="H3" t="n">
-        <v>-0.4312</v>
+        <v>-2.5986</v>
       </c>
       <c r="I3" t="n">
-        <v>0.4452</v>
+        <v>5.8372</v>
       </c>
       <c r="J3" t="n">
-        <v>0.5538</v>
+        <v>4.729</v>
       </c>
       <c r="K3" t="n">
-        <v>1.1909</v>
+        <v>-1.1763</v>
       </c>
       <c r="L3" t="n">
-        <v>-0.6371</v>
+        <v>5.9053</v>
       </c>
       <c r="M3" t="n">
-        <v>-0.5397999999999999</v>
+        <v>-1.4904</v>
       </c>
       <c r="N3" t="n">
-        <v>-1.6221</v>
+        <v>-1.4223</v>
       </c>
       <c r="O3" t="n">
-        <v>1.0823</v>
+        <v>-0.06809999999999999</v>
       </c>
       <c r="P3" t="n">
-        <v>1.361</v>
+        <v>-0.9105</v>
       </c>
       <c r="Q3" t="n">
-        <v>0</v>
+        <v>-2.2763</v>
       </c>
       <c r="R3" t="n">
-        <v>1.361</v>
+        <v>1.3658</v>
       </c>
       <c r="S3" t="n">
-        <v>1.143</v>
+        <v>0.5377999999999999</v>
       </c>
       <c r="T3" t="n">
-        <v>2.3288</v>
+        <v>0.2622</v>
       </c>
       <c r="U3" t="n">
-        <v>-1.1859</v>
+        <v>0.2755</v>
       </c>
       <c r="V3" t="n">
-        <v>0.7712</v>
+        <v>0.1578</v>
       </c>
       <c r="W3" t="n">
-        <v>1.0927</v>
+        <v>0.3155</v>
       </c>
       <c r="X3" t="n">
-        <v>-0.3214</v>
+        <v>-0.1578</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>X. CASTANEDA</t>
+          <t>A. PUSTOVYI</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,67 +721,67 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>2.2234</v>
+        <v>2.2424</v>
       </c>
       <c r="E4" t="n">
-        <v>2.2887</v>
+        <v>2.5537</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.0653</v>
+        <v>-0.3112</v>
       </c>
       <c r="G4" t="n">
-        <v>3.2637</v>
+        <v>0.008699999999999999</v>
       </c>
       <c r="H4" t="n">
-        <v>-2.587</v>
+        <v>-0.4444</v>
       </c>
       <c r="I4" t="n">
-        <v>5.8507</v>
+        <v>0.4532</v>
       </c>
       <c r="J4" t="n">
-        <v>4.7739</v>
+        <v>0.5239</v>
       </c>
       <c r="K4" t="n">
-        <v>-1.154</v>
+        <v>1.1646</v>
       </c>
       <c r="L4" t="n">
-        <v>5.9279</v>
+        <v>-0.6407</v>
       </c>
       <c r="M4" t="n">
-        <v>-1.5103</v>
+        <v>-0.5152</v>
       </c>
       <c r="N4" t="n">
-        <v>-1.433</v>
+        <v>-1.6091</v>
       </c>
       <c r="O4" t="n">
-        <v>-0.0772</v>
+        <v>1.0939</v>
       </c>
       <c r="P4" t="n">
-        <v>-0.9073</v>
+        <v>1.3658</v>
       </c>
       <c r="Q4" t="n">
-        <v>-2.2683</v>
+        <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>1.361</v>
+        <v>1.3658</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.2937</v>
+        <v>0.094</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.5383</v>
+        <v>0.9403</v>
       </c>
       <c r="U4" t="n">
-        <v>0.2447</v>
+        <v>-0.8463000000000001</v>
       </c>
       <c r="V4" t="n">
-        <v>0.1607</v>
+        <v>0.7739</v>
       </c>
       <c r="W4" t="n">
-        <v>0.3214</v>
+        <v>1.0895</v>
       </c>
       <c r="X4" t="n">
-        <v>-0.1607</v>
+        <v>-0.3155</v>
       </c>
     </row>
     <row r="5">
@@ -799,67 +799,67 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>0.8538</v>
+        <v>0.8953</v>
       </c>
       <c r="E5" t="n">
-        <v>1.0858</v>
+        <v>1.0353</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.232</v>
+        <v>-0.14</v>
       </c>
       <c r="G5" t="n">
-        <v>-2.4113</v>
+        <v>-2.4092</v>
       </c>
       <c r="H5" t="n">
-        <v>-2.9177</v>
+        <v>-2.9126</v>
       </c>
       <c r="I5" t="n">
-        <v>0.5064</v>
+        <v>0.5034</v>
       </c>
       <c r="J5" t="n">
-        <v>-1.8874</v>
+        <v>-1.9085</v>
       </c>
       <c r="K5" t="n">
-        <v>-1.4688</v>
+        <v>-1.4759</v>
       </c>
       <c r="L5" t="n">
-        <v>-0.4186</v>
+        <v>-0.4326</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.5239</v>
+        <v>-0.5007</v>
       </c>
       <c r="N5" t="n">
-        <v>-1.4489</v>
+        <v>-1.4367</v>
       </c>
       <c r="O5" t="n">
-        <v>0.925</v>
+        <v>0.9360000000000001</v>
       </c>
       <c r="P5" t="n">
-        <v>0.9073</v>
+        <v>0.9105</v>
       </c>
       <c r="Q5" t="n">
         <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>0.9073</v>
+        <v>0.9105</v>
       </c>
       <c r="S5" t="n">
-        <v>0.8794999999999999</v>
+        <v>0.9176</v>
       </c>
       <c r="T5" t="n">
-        <v>1.1735</v>
+        <v>1.1518</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.294</v>
+        <v>-0.2342</v>
       </c>
       <c r="V5" t="n">
-        <v>1.4783</v>
+        <v>1.4764</v>
       </c>
       <c r="W5" t="n">
-        <v>1.7997</v>
+        <v>1.792</v>
       </c>
       <c r="X5" t="n">
-        <v>-0.3214</v>
+        <v>-0.3155</v>
       </c>
     </row>
     <row r="6">
@@ -877,64 +877,64 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.1166</v>
+        <v>0.8356</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.1941</v>
+        <v>0.5741000000000001</v>
       </c>
       <c r="F6" t="n">
-        <v>0.0775</v>
+        <v>0.2614</v>
       </c>
       <c r="G6" t="n">
-        <v>-0.8781</v>
+        <v>-0.8799</v>
       </c>
       <c r="H6" t="n">
-        <v>-1.2885</v>
+        <v>-1.2895</v>
       </c>
       <c r="I6" t="n">
-        <v>0.4105</v>
+        <v>0.4096</v>
       </c>
       <c r="J6" t="n">
-        <v>-0.2796</v>
+        <v>-0.3082</v>
       </c>
       <c r="K6" t="n">
-        <v>0.1763</v>
+        <v>0.1616</v>
       </c>
       <c r="L6" t="n">
-        <v>-0.4559</v>
+        <v>-0.4698</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.5984</v>
+        <v>-0.5717</v>
       </c>
       <c r="N6" t="n">
-        <v>-1.4648</v>
+        <v>-1.4511</v>
       </c>
       <c r="O6" t="n">
-        <v>0.8663999999999999</v>
+        <v>0.8794999999999999</v>
       </c>
       <c r="P6" t="n">
         <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>-1.1342</v>
+        <v>-1.1382</v>
       </c>
       <c r="R6" t="n">
-        <v>1.1342</v>
+        <v>1.1382</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.3312</v>
+        <v>0.626</v>
       </c>
       <c r="T6" t="n">
-        <v>0.127</v>
+        <v>0.931</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.4582</v>
+        <v>-0.305</v>
       </c>
       <c r="V6" t="n">
-        <v>1.0927</v>
+        <v>1.0895</v>
       </c>
       <c r="W6" t="n">
-        <v>1.0927</v>
+        <v>1.0895</v>
       </c>
       <c r="X6" t="n">
         <v>0</v>
@@ -943,7 +943,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>M. UDEZE</t>
+          <t>A. BEST</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +955,73 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-1.029</v>
+        <v>-1.0582</v>
       </c>
       <c r="E7" t="n">
-        <v>0.0114</v>
+        <v>-0.6019</v>
       </c>
       <c r="F7" t="n">
-        <v>-1.0404</v>
+        <v>-0.4563</v>
       </c>
       <c r="G7" t="n">
-        <v>0.2336</v>
+        <v>-1.2728</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.7634</v>
+        <v>-1.9161</v>
       </c>
       <c r="I7" t="n">
-        <v>0.997</v>
+        <v>0.6433</v>
       </c>
       <c r="J7" t="n">
-        <v>-0.5878</v>
+        <v>-1.1588</v>
       </c>
       <c r="K7" t="n">
-        <v>-0.6998</v>
+        <v>-0.6516999999999999</v>
       </c>
       <c r="L7" t="n">
-        <v>0.112</v>
+        <v>-0.5071</v>
       </c>
       <c r="M7" t="n">
-        <v>0.8214</v>
+        <v>-0.1139</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.0636</v>
+        <v>-1.2643</v>
       </c>
       <c r="O7" t="n">
-        <v>0.885</v>
+        <v>1.1504</v>
       </c>
       <c r="P7" t="n">
-        <v>0.4537</v>
+        <v>1.1382</v>
       </c>
       <c r="Q7" t="n">
         <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>0.4537</v>
+        <v>1.1382</v>
       </c>
       <c r="S7" t="n">
-        <v>0.0835</v>
+        <v>0.008200000000000001</v>
       </c>
       <c r="T7" t="n">
-        <v>0.4386</v>
+        <v>0.3992</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.3551</v>
+        <v>-0.391</v>
       </c>
       <c r="V7" t="n">
-        <v>-1.7997</v>
+        <v>-0.9317</v>
       </c>
       <c r="W7" t="n">
-        <v>0.1607</v>
+        <v>0.1578</v>
       </c>
       <c r="X7" t="n">
-        <v>-1.9604</v>
+        <v>-1.0895</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>R. GUERRERO</t>
+          <t>M. UDEZE</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,73 +1033,73 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-1.2482</v>
+        <v>-1.2414</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.57</v>
+        <v>-0.3482</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.6783</v>
+        <v>-0.8932</v>
       </c>
       <c r="G8" t="n">
-        <v>-1.1524</v>
+        <v>0.2416</v>
       </c>
       <c r="H8" t="n">
-        <v>-1.5122</v>
+        <v>-0.7612</v>
       </c>
       <c r="I8" t="n">
-        <v>0.3599</v>
+        <v>1.0028</v>
       </c>
       <c r="J8" t="n">
-        <v>0.177</v>
+        <v>-0.5917</v>
       </c>
       <c r="K8" t="n">
-        <v>-0.4573</v>
+        <v>-0.7035</v>
       </c>
       <c r="L8" t="n">
-        <v>0.6344</v>
+        <v>0.1117</v>
       </c>
       <c r="M8" t="n">
-        <v>-1.3294</v>
+        <v>0.8333</v>
       </c>
       <c r="N8" t="n">
-        <v>-1.0549</v>
+        <v>-0.0578</v>
       </c>
       <c r="O8" t="n">
-        <v>-0.2745</v>
+        <v>0.8911</v>
       </c>
       <c r="P8" t="n">
-        <v>-1.8147</v>
+        <v>0.4553</v>
       </c>
       <c r="Q8" t="n">
-        <v>-2.2683</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>0.4537</v>
+        <v>0.4553</v>
       </c>
       <c r="S8" t="n">
-        <v>1.7188</v>
+        <v>-0.1462</v>
       </c>
       <c r="T8" t="n">
-        <v>1.5213</v>
+        <v>0.0858</v>
       </c>
       <c r="U8" t="n">
-        <v>0.1975</v>
+        <v>-0.232</v>
       </c>
       <c r="V8" t="n">
-        <v>0</v>
+        <v>-1.792</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>0.1578</v>
       </c>
       <c r="X8" t="n">
-        <v>0</v>
+        <v>-1.9497</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>A. BEST</t>
+          <t>C. ORTEGA</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,73 +1111,73 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-1.3395</v>
+        <v>-1.6559</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.8895999999999999</v>
+        <v>0.0405</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.4499</v>
+        <v>-1.6963</v>
       </c>
       <c r="G9" t="n">
-        <v>-1.2759</v>
+        <v>-0.9963</v>
       </c>
       <c r="H9" t="n">
-        <v>-1.9236</v>
+        <v>-1.126</v>
       </c>
       <c r="I9" t="n">
-        <v>0.6477000000000001</v>
+        <v>0.1297</v>
       </c>
       <c r="J9" t="n">
-        <v>-1.1411</v>
+        <v>0.6375999999999999</v>
       </c>
       <c r="K9" t="n">
-        <v>-0.6478</v>
+        <v>0.1239</v>
       </c>
       <c r="L9" t="n">
-        <v>-0.4932</v>
+        <v>0.5135999999999999</v>
       </c>
       <c r="M9" t="n">
-        <v>-0.1348</v>
+        <v>-1.6339</v>
       </c>
       <c r="N9" t="n">
-        <v>-1.2758</v>
+        <v>-1.2499</v>
       </c>
       <c r="O9" t="n">
-        <v>1.1409</v>
+        <v>-0.384</v>
       </c>
       <c r="P9" t="n">
-        <v>1.1342</v>
+        <v>-0.4553</v>
       </c>
       <c r="Q9" t="n">
-        <v>0</v>
+        <v>-1.1382</v>
       </c>
       <c r="R9" t="n">
-        <v>1.1342</v>
+        <v>0.6829</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.2659</v>
+        <v>0.8852</v>
       </c>
       <c r="T9" t="n">
-        <v>0.0907</v>
+        <v>0.5411</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.3566</v>
+        <v>0.3441</v>
       </c>
       <c r="V9" t="n">
-        <v>-0.9320000000000001</v>
+        <v>-1.0895</v>
       </c>
       <c r="W9" t="n">
-        <v>0.1607</v>
+        <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>-1.0927</v>
+        <v>-1.0895</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>C. ORTEGA</t>
+          <t>R. GUERRERO</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,67 +1189,67 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-1.9613</v>
+        <v>-1.9095</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.7431</v>
+        <v>-1.1486</v>
       </c>
       <c r="F10" t="n">
-        <v>-1.2182</v>
+        <v>-0.7609</v>
       </c>
       <c r="G10" t="n">
-        <v>-1.0005</v>
+        <v>-1.1487</v>
       </c>
       <c r="H10" t="n">
-        <v>-1.1284</v>
+        <v>-1.5108</v>
       </c>
       <c r="I10" t="n">
-        <v>0.128</v>
+        <v>0.3621</v>
       </c>
       <c r="J10" t="n">
-        <v>0.6512</v>
+        <v>0.1709</v>
       </c>
       <c r="K10" t="n">
-        <v>0.1314</v>
+        <v>-0.4621</v>
       </c>
       <c r="L10" t="n">
-        <v>0.5197000000000001</v>
+        <v>0.633</v>
       </c>
       <c r="M10" t="n">
-        <v>-1.6516</v>
+        <v>-1.3196</v>
       </c>
       <c r="N10" t="n">
-        <v>-1.2599</v>
+        <v>-1.0487</v>
       </c>
       <c r="O10" t="n">
-        <v>-0.3918</v>
+        <v>-0.271</v>
       </c>
       <c r="P10" t="n">
-        <v>-0.4537</v>
+        <v>-1.8211</v>
       </c>
       <c r="Q10" t="n">
-        <v>-1.1342</v>
+        <v>-2.2763</v>
       </c>
       <c r="R10" t="n">
-        <v>0.6805</v>
+        <v>0.4553</v>
       </c>
       <c r="S10" t="n">
-        <v>0.5855</v>
+        <v>1.0603</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.2601</v>
+        <v>0.9568</v>
       </c>
       <c r="U10" t="n">
-        <v>0.8456</v>
+        <v>0.1035</v>
       </c>
       <c r="V10" t="n">
-        <v>-1.0927</v>
+        <v>0</v>
       </c>
       <c r="W10" t="n">
         <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>-1.0927</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11">
@@ -1267,67 +1267,67 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-2.0684</v>
+        <v>-1.9992</v>
       </c>
       <c r="E11" t="n">
-        <v>1.3452</v>
+        <v>1.1543</v>
       </c>
       <c r="F11" t="n">
-        <v>-3.4136</v>
+        <v>-3.1534</v>
       </c>
       <c r="G11" t="n">
-        <v>1.6069</v>
+        <v>1.6109</v>
       </c>
       <c r="H11" t="n">
-        <v>0.218</v>
+        <v>0.2101</v>
       </c>
       <c r="I11" t="n">
-        <v>1.3888</v>
+        <v>1.4008</v>
       </c>
       <c r="J11" t="n">
-        <v>2.1784</v>
+        <v>2.1549</v>
       </c>
       <c r="K11" t="n">
-        <v>2.0292</v>
+        <v>2.006</v>
       </c>
       <c r="L11" t="n">
-        <v>0.1493</v>
+        <v>0.1489</v>
       </c>
       <c r="M11" t="n">
-        <v>-0.5716</v>
+        <v>-0.5441</v>
       </c>
       <c r="N11" t="n">
-        <v>-1.8112</v>
+        <v>-1.7959</v>
       </c>
       <c r="O11" t="n">
-        <v>1.2396</v>
+        <v>1.2518</v>
       </c>
       <c r="P11" t="n">
-        <v>0.2268</v>
+        <v>0.2276</v>
       </c>
       <c r="Q11" t="n">
-        <v>-1.1342</v>
+        <v>-1.1382</v>
       </c>
       <c r="R11" t="n">
-        <v>1.361</v>
+        <v>1.3658</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.07770000000000001</v>
+        <v>-0.0245</v>
       </c>
       <c r="T11" t="n">
-        <v>0.6866</v>
+        <v>0.5245</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.7643</v>
+        <v>-0.549</v>
       </c>
       <c r="V11" t="n">
-        <v>-3.8243</v>
+        <v>-3.8132</v>
       </c>
       <c r="W11" t="n">
-        <v>-0.3856</v>
+        <v>-0.387</v>
       </c>
       <c r="X11" t="n">
-        <v>-3.4387</v>
+        <v>-3.4262</v>
       </c>
     </row>
     <row r="12">
@@ -1345,67 +1345,67 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-8.880000000000001</v>
+        <v>-7.5097</v>
       </c>
       <c r="E12" t="n">
-        <v>-8.957000000000001</v>
+        <v>-7.5862</v>
       </c>
       <c r="F12" t="n">
-        <v>0.077</v>
+        <v>0.0765</v>
       </c>
       <c r="G12" t="n">
-        <v>-3.9984</v>
+        <v>-4.0242</v>
       </c>
       <c r="H12" t="n">
-        <v>-3.9477</v>
+        <v>-3.9627</v>
       </c>
       <c r="I12" t="n">
-        <v>-0.0507</v>
+        <v>-0.0616</v>
       </c>
       <c r="J12" t="n">
-        <v>-4.7595</v>
+        <v>-4.8145</v>
       </c>
       <c r="K12" t="n">
-        <v>-2.467</v>
+        <v>-2.4971</v>
       </c>
       <c r="L12" t="n">
-        <v>-2.2926</v>
+        <v>-2.3175</v>
       </c>
       <c r="M12" t="n">
-        <v>0.7611</v>
+        <v>0.7903</v>
       </c>
       <c r="N12" t="n">
-        <v>-1.4807</v>
+        <v>-1.4656</v>
       </c>
       <c r="O12" t="n">
-        <v>2.2418</v>
+        <v>2.2559</v>
       </c>
       <c r="P12" t="n">
-        <v>-2.0415</v>
+        <v>-2.0487</v>
       </c>
       <c r="Q12" t="n">
-        <v>-3.4025</v>
+        <v>-3.4145</v>
       </c>
       <c r="R12" t="n">
-        <v>1.361</v>
+        <v>1.3658</v>
       </c>
       <c r="S12" t="n">
-        <v>-1.9081</v>
+        <v>-0.5051</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.9557</v>
+        <v>0.485</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.9524</v>
+        <v>-0.9901</v>
       </c>
       <c r="V12" t="n">
-        <v>-0.9320000000000001</v>
+        <v>-0.9317</v>
       </c>
       <c r="W12" t="n">
-        <v>0.1607</v>
+        <v>0.1578</v>
       </c>
       <c r="X12" t="n">
-        <v>-1.0927</v>
+        <v>-1.0895</v>
       </c>
     </row>
     <row r="13">
@@ -1423,67 +1423,67 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-4.289300000000001</v>
+        <v>-2.896499999999999</v>
       </c>
       <c r="E13" t="n">
-        <v>1.911099999999999</v>
+        <v>3.011100000000001</v>
       </c>
       <c r="F13" t="n">
-        <v>-6.2005</v>
+        <v>-5.9075</v>
       </c>
       <c r="G13" t="n">
-        <v>-3.156700000000001</v>
+        <v>-3.178900000000001</v>
       </c>
       <c r="H13" t="n">
-        <v>-15.3381</v>
+        <v>-15.3642</v>
       </c>
       <c r="I13" t="n">
-        <v>12.1816</v>
+        <v>12.1853</v>
       </c>
       <c r="J13" t="n">
-        <v>1.2959</v>
+        <v>1.038900000000001</v>
       </c>
       <c r="K13" t="n">
-        <v>-1.6352</v>
+        <v>-1.7868</v>
       </c>
       <c r="L13" t="n">
-        <v>2.9312</v>
+        <v>2.8254</v>
       </c>
       <c r="M13" t="n">
-        <v>-4.4526</v>
+        <v>-4.2178</v>
       </c>
       <c r="N13" t="n">
-        <v>-13.7029</v>
+        <v>-13.5775</v>
       </c>
       <c r="O13" t="n">
-        <v>9.250200000000001</v>
+        <v>9.3597</v>
       </c>
       <c r="P13" t="n">
-        <v>0</v>
+        <v>-4.440892098500626e-16</v>
       </c>
       <c r="Q13" t="n">
-        <v>-11.3417</v>
+        <v>-11.3817</v>
       </c>
       <c r="R13" t="n">
-        <v>11.3418</v>
+        <v>11.3818</v>
       </c>
       <c r="S13" t="n">
-        <v>1.9205</v>
+        <v>3.3221</v>
       </c>
       <c r="T13" t="n">
-        <v>5.368500000000001</v>
+        <v>6.802200000000001</v>
       </c>
       <c r="U13" t="n">
-        <v>-3.448</v>
+        <v>-3.4802</v>
       </c>
       <c r="V13" t="n">
-        <v>-3.0532</v>
+        <v>-3.039300000000001</v>
       </c>
       <c r="W13" t="n">
-        <v>6.5883</v>
+        <v>6.5518</v>
       </c>
       <c r="X13" t="n">
-        <v>-9.641400000000001</v>
+        <v>-9.590999999999999</v>
       </c>
     </row>
     <row r="14">
@@ -1501,73 +1501,73 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>6.7238</v>
+        <v>5.3287</v>
       </c>
       <c r="E14" t="n">
-        <v>7.4358</v>
+        <v>6.0044</v>
       </c>
       <c r="F14" t="n">
-        <v>-0.712</v>
+        <v>-0.6757</v>
       </c>
       <c r="G14" t="n">
-        <v>2.6147</v>
+        <v>2.6282</v>
       </c>
       <c r="H14" t="n">
-        <v>2.2654</v>
+        <v>2.2688</v>
       </c>
       <c r="I14" t="n">
-        <v>0.3493</v>
+        <v>0.3594</v>
       </c>
       <c r="J14" t="n">
-        <v>2.7095</v>
+        <v>2.6972</v>
       </c>
       <c r="K14" t="n">
-        <v>2.5975</v>
+        <v>2.5855</v>
       </c>
       <c r="L14" t="n">
-        <v>0.112</v>
+        <v>0.1117</v>
       </c>
       <c r="M14" t="n">
-        <v>-0.0948</v>
+        <v>-0.06900000000000001</v>
       </c>
       <c r="N14" t="n">
-        <v>-0.3321</v>
+        <v>-0.3168</v>
       </c>
       <c r="O14" t="n">
-        <v>0.2373</v>
+        <v>0.2477</v>
       </c>
       <c r="P14" t="n">
-        <v>0.6805</v>
+        <v>0.6829</v>
       </c>
       <c r="Q14" t="n">
-        <v>-0.2268</v>
+        <v>-0.2276</v>
       </c>
       <c r="R14" t="n">
-        <v>0.9073</v>
+        <v>0.9105</v>
       </c>
       <c r="S14" t="n">
-        <v>2.4967</v>
+        <v>1.0859</v>
       </c>
       <c r="T14" t="n">
-        <v>2.6071</v>
+        <v>1.1981</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.1104</v>
+        <v>-0.1122</v>
       </c>
       <c r="V14" t="n">
-        <v>0.9320000000000001</v>
+        <v>0.9317</v>
       </c>
       <c r="W14" t="n">
-        <v>2.3461</v>
+        <v>2.3367</v>
       </c>
       <c r="X14" t="n">
-        <v>-1.4141</v>
+        <v>-1.405</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A. LEN</t>
+          <t>A. ABALDE</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,73 +1579,73 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>3.0327</v>
+        <v>2.9442</v>
       </c>
       <c r="E15" t="n">
-        <v>2.4613</v>
+        <v>1.9196</v>
       </c>
       <c r="F15" t="n">
-        <v>0.5715</v>
+        <v>1.0246</v>
       </c>
       <c r="G15" t="n">
-        <v>2.028</v>
+        <v>3.3252</v>
       </c>
       <c r="H15" t="n">
-        <v>2.681</v>
+        <v>2.5585</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.653</v>
+        <v>0.7665999999999999</v>
       </c>
       <c r="J15" t="n">
-        <v>2.6056</v>
+        <v>2.0454</v>
       </c>
       <c r="K15" t="n">
-        <v>2.4936</v>
+        <v>1.7409</v>
       </c>
       <c r="L15" t="n">
-        <v>0.112</v>
+        <v>0.3045</v>
       </c>
       <c r="M15" t="n">
-        <v>-0.5776</v>
+        <v>1.2798</v>
       </c>
       <c r="N15" t="n">
-        <v>0.1874</v>
+        <v>0.8176</v>
       </c>
       <c r="O15" t="n">
-        <v>-0.7649</v>
+        <v>0.4622</v>
       </c>
       <c r="P15" t="n">
-        <v>0.2268</v>
+        <v>1.5934</v>
       </c>
       <c r="Q15" t="n">
-        <v>-1.1342</v>
+        <v>0</v>
       </c>
       <c r="R15" t="n">
-        <v>1.361</v>
+        <v>1.5934</v>
       </c>
       <c r="S15" t="n">
-        <v>0.7779</v>
+        <v>-0.8849</v>
       </c>
       <c r="T15" t="n">
-        <v>0.6684</v>
+        <v>-0.1258</v>
       </c>
       <c r="U15" t="n">
-        <v>0.1095</v>
+        <v>-0.7592</v>
       </c>
       <c r="V15" t="n">
-        <v>0</v>
+        <v>-1.0895</v>
       </c>
       <c r="W15" t="n">
-        <v>0.3214</v>
+        <v>0</v>
       </c>
       <c r="X15" t="n">
-        <v>-0.3214</v>
+        <v>-1.0895</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>T. MALEDON</t>
+          <t>A. LEN</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,73 +1657,73 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>2.3398</v>
+        <v>2.3537</v>
       </c>
       <c r="E16" t="n">
-        <v>1.0369</v>
+        <v>1.9705</v>
       </c>
       <c r="F16" t="n">
-        <v>1.3029</v>
+        <v>0.3831</v>
       </c>
       <c r="G16" t="n">
-        <v>1.6363</v>
+        <v>2.0378</v>
       </c>
       <c r="H16" t="n">
-        <v>1.6709</v>
+        <v>2.6824</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.0346</v>
+        <v>-0.6446</v>
       </c>
       <c r="J16" t="n">
-        <v>0.5984</v>
+        <v>2.5938</v>
       </c>
       <c r="K16" t="n">
-        <v>0.7131</v>
+        <v>2.4821</v>
       </c>
       <c r="L16" t="n">
-        <v>-0.1147</v>
+        <v>0.1117</v>
       </c>
       <c r="M16" t="n">
-        <v>1.0379</v>
+        <v>-0.556</v>
       </c>
       <c r="N16" t="n">
-        <v>0.9578</v>
+        <v>0.2003</v>
       </c>
       <c r="O16" t="n">
-        <v>0.08</v>
+        <v>-0.7563</v>
       </c>
       <c r="P16" t="n">
-        <v>-0.6805</v>
+        <v>0.2276</v>
       </c>
       <c r="Q16" t="n">
-        <v>-2.2683</v>
+        <v>-1.1382</v>
       </c>
       <c r="R16" t="n">
-        <v>1.5878</v>
+        <v>1.3658</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.1909</v>
+        <v>0.0882</v>
       </c>
       <c r="T16" t="n">
-        <v>0.0393</v>
+        <v>0.1994</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.2302</v>
+        <v>-0.1111</v>
       </c>
       <c r="V16" t="n">
-        <v>1.5748</v>
+        <v>0</v>
       </c>
       <c r="W16" t="n">
-        <v>2.6675</v>
+        <v>0.3155</v>
       </c>
       <c r="X16" t="n">
-        <v>-1.0927</v>
+        <v>-0.3155</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A. ABALDE</t>
+          <t>T. MALEDON</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,73 +1735,73 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>1.7633</v>
+        <v>2.3233</v>
       </c>
       <c r="E17" t="n">
-        <v>1.2393</v>
+        <v>1.1124</v>
       </c>
       <c r="F17" t="n">
-        <v>0.524</v>
+        <v>1.2109</v>
       </c>
       <c r="G17" t="n">
-        <v>3.3278</v>
+        <v>1.6419</v>
       </c>
       <c r="H17" t="n">
-        <v>2.5496</v>
+        <v>1.6715</v>
       </c>
       <c r="I17" t="n">
-        <v>0.7782</v>
+        <v>-0.0296</v>
       </c>
       <c r="J17" t="n">
-        <v>2.074</v>
+        <v>0.5766</v>
       </c>
       <c r="K17" t="n">
-        <v>1.749</v>
+        <v>0.696</v>
       </c>
       <c r="L17" t="n">
-        <v>0.325</v>
+        <v>-0.1194</v>
       </c>
       <c r="M17" t="n">
-        <v>1.2538</v>
+        <v>1.0653</v>
       </c>
       <c r="N17" t="n">
-        <v>0.8006</v>
+        <v>0.9755</v>
       </c>
       <c r="O17" t="n">
-        <v>0.4532</v>
+        <v>0.0898</v>
       </c>
       <c r="P17" t="n">
-        <v>1.5878</v>
+        <v>-0.6829</v>
       </c>
       <c r="Q17" t="n">
-        <v>0</v>
+        <v>-2.2763</v>
       </c>
       <c r="R17" t="n">
-        <v>1.5878</v>
+        <v>1.5934</v>
       </c>
       <c r="S17" t="n">
-        <v>-2.0596</v>
+        <v>-0.1985</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.8347</v>
+        <v>0.1599</v>
       </c>
       <c r="U17" t="n">
-        <v>-1.2249</v>
+        <v>-0.3584</v>
       </c>
       <c r="V17" t="n">
-        <v>-1.0927</v>
+        <v>1.5628</v>
       </c>
       <c r="W17" t="n">
-        <v>0</v>
+        <v>2.6522</v>
       </c>
       <c r="X17" t="n">
-        <v>-1.0927</v>
+        <v>-1.0895</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>C. OKEKE</t>
+          <t>S. LLULL</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1813,73 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>1.2688</v>
+        <v>1.2804</v>
       </c>
       <c r="E18" t="n">
-        <v>1.8258</v>
+        <v>2.3585</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.5570000000000001</v>
+        <v>-1.0781</v>
       </c>
       <c r="G18" t="n">
-        <v>1.7575</v>
+        <v>-0.0019</v>
       </c>
       <c r="H18" t="n">
-        <v>1.0751</v>
+        <v>1.5504</v>
       </c>
       <c r="I18" t="n">
-        <v>0.6824</v>
+        <v>-1.5523</v>
       </c>
       <c r="J18" t="n">
-        <v>1.1755</v>
+        <v>1.2972</v>
       </c>
       <c r="K18" t="n">
-        <v>0.7304</v>
+        <v>1.5513</v>
       </c>
       <c r="L18" t="n">
-        <v>0.4451</v>
+        <v>-0.2541</v>
       </c>
       <c r="M18" t="n">
-        <v>0.582</v>
+        <v>-1.2992</v>
       </c>
       <c r="N18" t="n">
-        <v>0.3446</v>
+        <v>-0.0009</v>
       </c>
       <c r="O18" t="n">
-        <v>0.2373</v>
+        <v>-1.2982</v>
       </c>
       <c r="P18" t="n">
-        <v>0.6805</v>
+        <v>-0.4553</v>
       </c>
       <c r="Q18" t="n">
-        <v>-0.2268</v>
+        <v>-1.3658</v>
       </c>
       <c r="R18" t="n">
-        <v>0.9073</v>
+        <v>0.9105</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.0765</v>
+        <v>-0.4414</v>
       </c>
       <c r="T18" t="n">
-        <v>0.8771</v>
+        <v>0.2481</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.9536</v>
+        <v>-0.6895</v>
       </c>
       <c r="V18" t="n">
-        <v>-1.0927</v>
+        <v>2.1789</v>
       </c>
       <c r="W18" t="n">
-        <v>0</v>
+        <v>2.1789</v>
       </c>
       <c r="X18" t="n">
-        <v>-1.0927</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>T. LYLES</t>
+          <t>C. OKEKE</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,73 +1891,73 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>0.5899</v>
+        <v>1.1718</v>
       </c>
       <c r="E19" t="n">
-        <v>0.439</v>
+        <v>1.4517</v>
       </c>
       <c r="F19" t="n">
-        <v>0.1509</v>
+        <v>-0.2798</v>
       </c>
       <c r="G19" t="n">
-        <v>-0.3372</v>
+        <v>1.7584</v>
       </c>
       <c r="H19" t="n">
-        <v>-0.3319</v>
+        <v>1.0715</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.0053</v>
+        <v>0.6869</v>
       </c>
       <c r="J19" t="n">
-        <v>-0.1996</v>
+        <v>1.1524</v>
       </c>
       <c r="K19" t="n">
-        <v>-0.6447000000000001</v>
+        <v>0.7131999999999999</v>
       </c>
       <c r="L19" t="n">
-        <v>0.4451</v>
+        <v>0.4392</v>
       </c>
       <c r="M19" t="n">
-        <v>-0.1375</v>
+        <v>0.606</v>
       </c>
       <c r="N19" t="n">
-        <v>0.3129</v>
+        <v>0.3583</v>
       </c>
       <c r="O19" t="n">
-        <v>-0.4504</v>
+        <v>0.2477</v>
       </c>
       <c r="P19" t="n">
-        <v>0</v>
+        <v>0.6829</v>
       </c>
       <c r="Q19" t="n">
-        <v>-1.1342</v>
+        <v>-0.2276</v>
       </c>
       <c r="R19" t="n">
-        <v>1.1342</v>
+        <v>0.9105</v>
       </c>
       <c r="S19" t="n">
-        <v>1.2485</v>
+        <v>-0.18</v>
       </c>
       <c r="T19" t="n">
-        <v>1.612</v>
+        <v>0.5269</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.3636</v>
+        <v>-0.7069</v>
       </c>
       <c r="V19" t="n">
-        <v>-0.3214</v>
+        <v>-1.0895</v>
       </c>
       <c r="W19" t="n">
-        <v>0.1607</v>
+        <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>-0.4822</v>
+        <v>-1.0895</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>S. LLULL</t>
+          <t>T. LYLES</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,67 +1969,67 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.248</v>
+        <v>-0.2412</v>
       </c>
       <c r="E20" t="n">
-        <v>1.3315</v>
+        <v>-0.649</v>
       </c>
       <c r="F20" t="n">
-        <v>-1.5796</v>
+        <v>0.4078</v>
       </c>
       <c r="G20" t="n">
-        <v>-0.0078</v>
+        <v>-0.3344</v>
       </c>
       <c r="H20" t="n">
-        <v>1.5409</v>
+        <v>-0.3331</v>
       </c>
       <c r="I20" t="n">
-        <v>-1.5487</v>
+        <v>-0.0013</v>
       </c>
       <c r="J20" t="n">
-        <v>1.3238</v>
+        <v>-0.2233</v>
       </c>
       <c r="K20" t="n">
-        <v>1.5585</v>
+        <v>-0.6625</v>
       </c>
       <c r="L20" t="n">
-        <v>-0.2347</v>
+        <v>0.4392</v>
       </c>
       <c r="M20" t="n">
-        <v>-1.3316</v>
+        <v>-0.1111</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.0176</v>
+        <v>0.3294</v>
       </c>
       <c r="O20" t="n">
-        <v>-1.314</v>
+        <v>-0.4405</v>
       </c>
       <c r="P20" t="n">
-        <v>-0.4537</v>
+        <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>-1.361</v>
+        <v>-1.1382</v>
       </c>
       <c r="R20" t="n">
-        <v>0.9073</v>
+        <v>1.1382</v>
       </c>
       <c r="S20" t="n">
-        <v>-1.9719</v>
+        <v>0.4087</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.8166</v>
+        <v>0.5547</v>
       </c>
       <c r="U20" t="n">
-        <v>-1.1553</v>
+        <v>-0.146</v>
       </c>
       <c r="V20" t="n">
-        <v>2.1853</v>
+        <v>-0.3155</v>
       </c>
       <c r="W20" t="n">
-        <v>2.1853</v>
+        <v>0.1578</v>
       </c>
       <c r="X20" t="n">
-        <v>0</v>
+        <v>-0.4733</v>
       </c>
     </row>
     <row r="21">
@@ -2047,58 +2047,58 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-1.5595</v>
+        <v>-1.0428</v>
       </c>
       <c r="E21" t="n">
-        <v>-2.1295</v>
+        <v>-1.9047</v>
       </c>
       <c r="F21" t="n">
-        <v>0.5699</v>
+        <v>0.8619</v>
       </c>
       <c r="G21" t="n">
-        <v>-1.398</v>
+        <v>-1.4006</v>
       </c>
       <c r="H21" t="n">
-        <v>0.945</v>
+        <v>0.9504</v>
       </c>
       <c r="I21" t="n">
-        <v>-2.3431</v>
+        <v>-2.351</v>
       </c>
       <c r="J21" t="n">
-        <v>-1.9208</v>
+        <v>-1.9325</v>
       </c>
       <c r="K21" t="n">
-        <v>0.3637</v>
+        <v>0.362</v>
       </c>
       <c r="L21" t="n">
-        <v>-2.2844</v>
+        <v>-2.2945</v>
       </c>
       <c r="M21" t="n">
-        <v>0.5228</v>
+        <v>0.5319</v>
       </c>
       <c r="N21" t="n">
-        <v>0.5814</v>
+        <v>0.5884</v>
       </c>
       <c r="O21" t="n">
-        <v>-0.0586</v>
+        <v>-0.0565</v>
       </c>
       <c r="P21" t="n">
-        <v>0.6805</v>
+        <v>0.6829</v>
       </c>
       <c r="Q21" t="n">
         <v>0</v>
       </c>
       <c r="R21" t="n">
-        <v>0.6805</v>
+        <v>0.6829</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.842</v>
+        <v>-0.3251</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.2087</v>
+        <v>0.0278</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.6333</v>
+        <v>-0.3529</v>
       </c>
       <c r="V21" t="n">
         <v>0</v>
@@ -2113,7 +2113,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>G. PROCIDA</t>
+          <t>A. FELIZ</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,64 +2125,64 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-2.2041</v>
+        <v>-1.3657</v>
       </c>
       <c r="E22" t="n">
-        <v>-2.6458</v>
+        <v>-0.5598</v>
       </c>
       <c r="F22" t="n">
-        <v>0.4418</v>
+        <v>-0.8058999999999999</v>
       </c>
       <c r="G22" t="n">
-        <v>-2.6468</v>
+        <v>-1.7862</v>
       </c>
       <c r="H22" t="n">
-        <v>0.4213</v>
+        <v>1.126</v>
       </c>
       <c r="I22" t="n">
-        <v>-3.0681</v>
+        <v>-2.9121</v>
       </c>
       <c r="J22" t="n">
-        <v>-2.7964</v>
+        <v>-0.513</v>
       </c>
       <c r="K22" t="n">
-        <v>0.3117</v>
+        <v>1.7442</v>
       </c>
       <c r="L22" t="n">
-        <v>-3.1081</v>
+        <v>-2.2572</v>
       </c>
       <c r="M22" t="n">
-        <v>0.1496</v>
+        <v>-1.2731</v>
       </c>
       <c r="N22" t="n">
-        <v>0.1096</v>
+        <v>-0.6182</v>
       </c>
       <c r="O22" t="n">
-        <v>0.04</v>
+        <v>-0.6549</v>
       </c>
       <c r="P22" t="n">
-        <v>0.6805</v>
+        <v>0.4553</v>
       </c>
       <c r="Q22" t="n">
-        <v>0</v>
+        <v>-0.2276</v>
       </c>
       <c r="R22" t="n">
-        <v>0.6805</v>
+        <v>0.6829</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.9448</v>
+        <v>-0.0349</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.5565</v>
+        <v>0.1808</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.3883</v>
+        <v>-0.2157</v>
       </c>
       <c r="V22" t="n">
-        <v>0.7071</v>
+        <v>0</v>
       </c>
       <c r="W22" t="n">
-        <v>0.7071</v>
+        <v>0</v>
       </c>
       <c r="X22" t="n">
         <v>0</v>
@@ -2191,7 +2191,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A. FELIZ</t>
+          <t>G. PROCIDA</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2203,64 +2203,64 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-2.4044</v>
+        <v>-1.7331</v>
       </c>
       <c r="E23" t="n">
-        <v>-1.4799</v>
+        <v>-2.3109</v>
       </c>
       <c r="F23" t="n">
-        <v>-0.9245</v>
+        <v>0.5777</v>
       </c>
       <c r="G23" t="n">
-        <v>-1.785</v>
+        <v>-2.6516</v>
       </c>
       <c r="H23" t="n">
-        <v>1.1284</v>
+        <v>0.4249</v>
       </c>
       <c r="I23" t="n">
-        <v>-2.9134</v>
+        <v>-3.0764</v>
       </c>
       <c r="J23" t="n">
-        <v>-0.4879</v>
+        <v>-2.8111</v>
       </c>
       <c r="K23" t="n">
-        <v>1.7592</v>
+        <v>0.3103</v>
       </c>
       <c r="L23" t="n">
-        <v>-2.2471</v>
+        <v>-3.1213</v>
       </c>
       <c r="M23" t="n">
-        <v>-1.2971</v>
+        <v>0.1595</v>
       </c>
       <c r="N23" t="n">
-        <v>-0.6308</v>
+        <v>0.1146</v>
       </c>
       <c r="O23" t="n">
-        <v>-0.6663</v>
+        <v>0.0449</v>
       </c>
       <c r="P23" t="n">
-        <v>0.4537</v>
+        <v>0.6829</v>
       </c>
       <c r="Q23" t="n">
-        <v>-0.2268</v>
+        <v>0</v>
       </c>
       <c r="R23" t="n">
-        <v>0.6805</v>
+        <v>0.6829</v>
       </c>
       <c r="S23" t="n">
-        <v>-1.0731</v>
+        <v>-0.467</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.7652</v>
+        <v>-0.2023</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.3079</v>
+        <v>-0.2647</v>
       </c>
       <c r="V23" t="n">
-        <v>0</v>
+        <v>0.7025</v>
       </c>
       <c r="W23" t="n">
-        <v>0</v>
+        <v>0.7025</v>
       </c>
       <c r="X23" t="n">
         <v>0</v>
@@ -2281,67 +2281,67 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-5.013</v>
+        <v>-5.1495</v>
       </c>
       <c r="E24" t="n">
-        <v>-3.3138</v>
+        <v>-3.4854</v>
       </c>
       <c r="F24" t="n">
-        <v>-1.6991</v>
+        <v>-1.6641</v>
       </c>
       <c r="G24" t="n">
-        <v>-2.0328</v>
+        <v>-2.0379</v>
       </c>
       <c r="H24" t="n">
-        <v>1.3924</v>
+        <v>1.3929</v>
       </c>
       <c r="I24" t="n">
-        <v>-3.4252</v>
+        <v>-3.4308</v>
       </c>
       <c r="J24" t="n">
-        <v>-0.6294</v>
+        <v>-0.665</v>
       </c>
       <c r="K24" t="n">
-        <v>2.0709</v>
+        <v>2.0544</v>
       </c>
       <c r="L24" t="n">
-        <v>-2.7003</v>
+        <v>-2.7194</v>
       </c>
       <c r="M24" t="n">
-        <v>-1.4034</v>
+        <v>-1.3729</v>
       </c>
       <c r="N24" t="n">
-        <v>-0.6785</v>
+        <v>-0.6615</v>
       </c>
       <c r="O24" t="n">
-        <v>-0.7249</v>
+        <v>-0.7114</v>
       </c>
       <c r="P24" t="n">
-        <v>-3.8562</v>
+        <v>-3.8697</v>
       </c>
       <c r="Q24" t="n">
-        <v>-4.7635</v>
+        <v>-4.7803</v>
       </c>
       <c r="R24" t="n">
-        <v>0.9073</v>
+        <v>0.9105</v>
       </c>
       <c r="S24" t="n">
-        <v>0.7153</v>
+        <v>0.6004</v>
       </c>
       <c r="T24" t="n">
-        <v>0.8257</v>
+        <v>0.7126</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.1104</v>
+        <v>-0.1122</v>
       </c>
       <c r="V24" t="n">
-        <v>0.1607</v>
+        <v>0.1578</v>
       </c>
       <c r="W24" t="n">
-        <v>1.2534</v>
+        <v>1.2472</v>
       </c>
       <c r="X24" t="n">
-        <v>-1.0927</v>
+        <v>-1.0895</v>
       </c>
     </row>
     <row r="25">
@@ -2359,67 +2359,67 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>4.289299999999999</v>
+        <v>5.8698</v>
       </c>
       <c r="E25" t="n">
-        <v>6.2006</v>
+        <v>5.907300000000001</v>
       </c>
       <c r="F25" t="n">
-        <v>-1.9112</v>
+        <v>-0.03759999999999986</v>
       </c>
       <c r="G25" t="n">
-        <v>3.1567</v>
+        <v>3.178899999999998</v>
       </c>
       <c r="H25" t="n">
-        <v>15.3381</v>
+        <v>15.3642</v>
       </c>
       <c r="I25" t="n">
-        <v>-12.1815</v>
+        <v>-12.1852</v>
       </c>
       <c r="J25" t="n">
-        <v>4.452699999999998</v>
+        <v>4.2177</v>
       </c>
       <c r="K25" t="n">
-        <v>13.7029</v>
+        <v>13.5774</v>
       </c>
       <c r="L25" t="n">
-        <v>-9.2501</v>
+        <v>-9.3596</v>
       </c>
       <c r="M25" t="n">
-        <v>-1.2959</v>
+        <v>-1.0388</v>
       </c>
       <c r="N25" t="n">
-        <v>1.6353</v>
+        <v>1.7867</v>
       </c>
       <c r="O25" t="n">
-        <v>-2.9313</v>
+        <v>-2.8255</v>
       </c>
       <c r="P25" t="n">
-        <v>-0.000100000000000211</v>
+        <v>0</v>
       </c>
       <c r="Q25" t="n">
-        <v>-11.3416</v>
+        <v>-11.3816</v>
       </c>
       <c r="R25" t="n">
-        <v>11.3415</v>
+        <v>11.3815</v>
       </c>
       <c r="S25" t="n">
-        <v>-1.9204</v>
+        <v>-0.3485999999999998</v>
       </c>
       <c r="T25" t="n">
-        <v>3.4479</v>
+        <v>3.4802</v>
       </c>
       <c r="U25" t="n">
-        <v>-5.3684</v>
+        <v>-3.8288</v>
       </c>
       <c r="V25" t="n">
-        <v>3.0531</v>
+        <v>3.0392</v>
       </c>
       <c r="W25" t="n">
-        <v>9.641500000000001</v>
+        <v>9.5908</v>
       </c>
       <c r="X25" t="n">
-        <v>-6.5885</v>
+        <v>-6.5518</v>
       </c>
     </row>
   </sheetData>

--- a/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104593_W15.xlsx
+++ b/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104593_W15.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X25"/>
+  <dimension ref="A1:Y25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -549,6 +549,11 @@
           <t>Def_FT</t>
         </is>
       </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>Game_File</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -627,6 +632,11 @@
       <c r="X2" t="n">
         <v>-0.1578</v>
       </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>play_by_play_104593_W15.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -705,6 +715,11 @@
       <c r="X3" t="n">
         <v>-0.1578</v>
       </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>play_by_play_104593_W15.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -783,6 +798,11 @@
       <c r="X4" t="n">
         <v>-0.3155</v>
       </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>play_by_play_104593_W15.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -861,6 +881,11 @@
       <c r="X5" t="n">
         <v>-0.3155</v>
       </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>play_by_play_104593_W15.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -939,6 +964,11 @@
       <c r="X6" t="n">
         <v>0</v>
       </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>play_by_play_104593_W15.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1017,6 +1047,11 @@
       <c r="X7" t="n">
         <v>-1.0895</v>
       </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>play_by_play_104593_W15.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1095,6 +1130,11 @@
       <c r="X8" t="n">
         <v>-1.9497</v>
       </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>play_by_play_104593_W15.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1173,6 +1213,11 @@
       <c r="X9" t="n">
         <v>-1.0895</v>
       </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>play_by_play_104593_W15.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1251,6 +1296,11 @@
       <c r="X10" t="n">
         <v>0</v>
       </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>play_by_play_104593_W15.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1329,6 +1379,11 @@
       <c r="X11" t="n">
         <v>-3.4262</v>
       </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>play_by_play_104593_W15.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1407,6 +1462,11 @@
       <c r="X12" t="n">
         <v>-1.0895</v>
       </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>play_by_play_104593_W15.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1485,6 +1545,7 @@
       <c r="X13" t="n">
         <v>-9.590999999999999</v>
       </c>
+      <c r="Y13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1563,6 +1624,11 @@
       <c r="X14" t="n">
         <v>-1.405</v>
       </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>play_by_play_104593_W15.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1641,6 +1707,11 @@
       <c r="X15" t="n">
         <v>-1.0895</v>
       </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>play_by_play_104593_W15.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1719,6 +1790,11 @@
       <c r="X16" t="n">
         <v>-0.3155</v>
       </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>play_by_play_104593_W15.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1797,6 +1873,11 @@
       <c r="X17" t="n">
         <v>-1.0895</v>
       </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>play_by_play_104593_W15.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1875,6 +1956,11 @@
       <c r="X18" t="n">
         <v>0</v>
       </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>play_by_play_104593_W15.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1953,6 +2039,11 @@
       <c r="X19" t="n">
         <v>-1.0895</v>
       </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>play_by_play_104593_W15.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -2031,6 +2122,11 @@
       <c r="X20" t="n">
         <v>-0.4733</v>
       </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>play_by_play_104593_W15.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -2109,6 +2205,11 @@
       <c r="X21" t="n">
         <v>0</v>
       </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>play_by_play_104593_W15.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -2187,6 +2288,11 @@
       <c r="X22" t="n">
         <v>0</v>
       </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>play_by_play_104593_W15.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -2265,6 +2371,11 @@
       <c r="X23" t="n">
         <v>0</v>
       </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>play_by_play_104593_W15.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -2343,6 +2454,11 @@
       <c r="X24" t="n">
         <v>-1.0895</v>
       </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>play_by_play_104593_W15.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -2421,6 +2537,7 @@
       <c r="X25" t="n">
         <v>-6.5518</v>
       </c>
+      <c r="Y25" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
